--- a/script_dictionary.xlsx
+++ b/script_dictionary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\Midterm-Project-DADS7202\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T00229\Documents\GitHub\Midterm-Project-DADS7202\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE494A2-59DC-4F35-B24A-02FAF4F09304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7015BEC-0136-47EE-92C1-29E393A648C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{F27542FC-4030-45BF-987C-3B033316C9F2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F27542FC-4030-45BF-987C-3B033316C9F2}"/>
   </bookViews>
   <sheets>
     <sheet name="script_dictionary" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -156,7 +159,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -166,7 +169,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -179,7 +182,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -189,7 +192,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -214,7 +217,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -224,7 +227,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -240,7 +243,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -250,7 +253,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -266,7 +269,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -276,7 +279,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -295,7 +298,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -305,7 +308,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -324,7 +327,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -334,7 +337,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -352,7 +355,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -368,7 +371,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -378,7 +381,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -394,7 +397,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -404,7 +407,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -420,7 +423,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -430,7 +433,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -441,7 +444,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -451,7 +454,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -470,7 +473,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -480,7 +483,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -491,7 +494,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -501,7 +504,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -526,7 +529,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -536,7 +539,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Tahoma"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -558,7 +561,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -566,7 +569,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -664,9 +667,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -704,7 +707,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -810,7 +813,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -952,7 +955,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -961,16 +964,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{780F9BA2-AF22-4FDB-95A9-B86132E70F3A}">
   <dimension ref="A1:E27"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.3125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="12.9375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.1875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="106.125" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="113.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -987,24 +990,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>8</v>
       </c>
@@ -1012,135 +1015,135 @@
         <v>7</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="27" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>8</v>
       </c>
@@ -1148,220 +1151,220 @@
         <v>7</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>19</v>
       </c>
       <c r="E11" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>19</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>31</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E20" s="12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E20" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>19</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>40</v>
       </c>
@@ -1378,7 +1381,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>40</v>
       </c>
@@ -1395,7 +1398,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>40</v>
       </c>
@@ -1412,25 +1415,28 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>71</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E21" xr:uid="{780F9BA2-AF22-4FDB-95A9-B86132E70F3A}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E27">
+    <sortCondition ref="D1:D27"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/script_dictionary.xlsx
+++ b/script_dictionary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T00229\Documents\GitHub\Midterm-Project-DADS7202\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7015BEC-0136-47EE-92C1-29E393A648C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A87578-9624-4C8C-B74D-5D35E0994594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F27542FC-4030-45BF-987C-3B033316C9F2}"/>
   </bookViews>
